--- a/business_surveys/049_jira_integration_feedback_form--business_surveys.xlsx
+++ b/business_surveys/049_jira_integration_feedback_form--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Form Category 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Form Category 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_comments</t>
+          <t>form_comments_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Form Comments 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -822,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,7 +901,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -918,7 +918,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,7 +952,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -969,7 +969,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1042,46 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>form_rating_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>form_rating_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
